--- a/series_data/the-vast/series_log.xlsx
+++ b/series_data/the-vast/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,6 +594,116 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep01/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c13ce9d360ff35282049c10068dc97dc_1784131162.mp4</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/084ff88a2503d38cde84277c1063f996_1784131341.mp4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep02/shots/shot_02.mp4</t>
         </is>
       </c>
     </row>

--- a/series_data/the-vast/series_log.xlsx
+++ b/series_data/the-vast/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,6 +704,202 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:57</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:56</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ee1cac47101b8bb375539f101cbfcc3c_1784303733.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1bbde9ae11fdd115184af4c97e4b6f90_1784303943.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep03/shots/shot_02.mp4</t>
         </is>
       </c>
     </row>

--- a/series_data/the-vast/series_log.xlsx
+++ b/series_data/the-vast/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +900,116 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-18 15:30</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/68384568c0e9052b1d09408eefffa74b_1784388622.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-18 15:36</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/34543c554cdd5f443f05fb8f8955c6b8_1784388797.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep04/shots/shot_02.mp4</t>
         </is>
       </c>
     </row>
